--- a/metodos_aprovados/arquivados_legado/Sinais_Metodos_Aprovados_2026-08-26.xlsx
+++ b/metodos_aprovados/arquivados_legado/Sinais_Metodos_Aprovados_2026-08-26.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/21df80ec97692de0/Documentos/GitHub/ARKAD_PROD/metodos_aprovados/arquivados_legado/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="19" documentId="11_2B59D187542A3A6CE3BA301159E338F74939EDA7" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B14E297F-34B8-463F-8E79-237BBB270B7E}"/>
